--- a/Financeiro_Report.xlsx
+++ b/Financeiro_Report.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI7"/>
+  <dimension ref="A1:AI13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -539,12 +539,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17495</t>
+          <t>550</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -554,59 +554,59 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>3918786000010380004</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4670</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>3865</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>3918786000010367048</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>08-Jun-2026</t>
@@ -624,32 +624,32 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>3918786000010295026</t>
+          <t>3918786000010295044</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -681,84 +681,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10900</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3135</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>9125</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1595</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>7265</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>3918786000010380002</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>7430</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>3918786000010367046</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Investiu 160 na compra de formas novas</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>08-Jun-2026</t>
@@ -791,17 +786,17 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>3918786000010295054</t>
+          <t>3918786000010295062</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -833,84 +828,79 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>5480</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3530</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1680</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>3918786000010379008</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>3918786000010358004</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Trabalhar na visibilidade do negócio (fazer um plano de postagem)</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>09-Jun-2026</t>
@@ -943,22 +933,22 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>3918786000010295012</t>
+          <t>3918786000010295042</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -990,12 +980,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1025,17 +1015,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11150</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3918786000010358002</t>
+          <t>3918786000010379006</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1075,37 +1065,37 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>3918786000010295052</t>
+          <t>3918786000010295056</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1137,12 +1127,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1172,17 +1162,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>3918786000010356002</t>
+          <t>3918786000010379004</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1222,37 +1212,37 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>3918786000010295090</t>
+          <t>3918786000010295040</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1284,140 +1274,1032 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8410</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>3918786000010379002</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>3918786000010287026</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3918786000010295058</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>17495</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>8960</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4670</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>3865</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>3918786000010367048</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>3918786000010295026</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>9125</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1595</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>7430</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>3918786000010367046</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Investiu 160 na compra de formas novas</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>3918786000010295054</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>KHADYA AMADE SILIMO</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>KHADYA AMADE SILIMO</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>3918786000010358004</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Trabalhar na visibilidade do negócio (fazer um plano de postagem)</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>09-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>3918786000010295012</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>ASSINA ABDALA ABDULSATAR</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>ASSINA ABDALA ABDULSATAR</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>18500</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5850</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>11150</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>3918786000010358002</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>3918786000010295052</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>JESSICA MARIA JOSE NAMUE</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>JESSICA MARIA JOSE NAMUE</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>3918786000010356002</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>3918786000010287028</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>3918786000010295090</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>TEODORA MANUEL BRAS</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>TEODORA MANUEL BRAS</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>13160</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>3705</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>PAM VERDE</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>3918786000004909039</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>PAM VERDE</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>1005</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>8450</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>3918786000010353002</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>3918786000004909063</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>NAMPULA</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>NAMPULA</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>08-Jun-2026</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Luisa</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Primeiro Mes de Implementação</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>3918786000010287030</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>3918786000010295028</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD13" t="inlineStr">
         <is>
           <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>Segunda Semana</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AG13" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AH13" t="inlineStr">
         <is>
           <t>3918786000007161003</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AI13" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -1684,13 +2566,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C33FBEF9-25CF-4864-8DD6-5F9868819C6F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CD4CB22-937A-4AD3-8C0C-05205B420FA5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31F53817-F3F2-44DA-844D-137AE8E85677}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{690BED69-35F3-4FCA-9E13-D9C12FB24CD3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85C49728-021E-4561-BD4F-FC97434E8FE2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55066A03-7AEC-4FA6-9D71-5E914A78F918}"/>
 </file>
--- a/Financeiro_Report.xlsx
+++ b/Financeiro_Report.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI13"/>
+  <dimension ref="A1:AI21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -539,7 +539,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>350</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -579,12 +579,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>350</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>3918786000010380004</t>
+          <t>3918786000010395008</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -624,37 +624,37 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>3918786000010295044</t>
+          <t>3918786000010295056</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>GRACA CHICO PAULO VAGOS</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>GRACA CHICO PAULO VAGOS</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -686,12 +686,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>33900</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -721,17 +721,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>22900</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3918786000010380002</t>
+          <t>3918786000010395006</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -786,22 +786,22 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>3918786000010295062</t>
+          <t>3918786000010295018</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -868,17 +868,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>35400</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3918786000010379008</t>
+          <t>3918786000010395004</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -933,17 +933,17 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>3918786000010295042</t>
+          <t>3918786000010295018</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1015,17 +1015,22 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>-235</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">teve prejuízo na semana porque estava ocupada e nao conseguiu produzir </t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3918786000010379006</t>
+          <t>3918786000010395002</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1050,7 +1055,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1065,37 +1070,37 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>3918786000010295056</t>
+          <t>3918786000010295042</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1127,12 +1132,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10130</t>
+          <t>600</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1162,17 +1167,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>90</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>3918786000010379004</t>
+          <t>3918786000010390008</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1197,7 +1202,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1227,22 +1232,22 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>3918786000010295040</t>
+          <t>3918786000010295012</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>ASSINA ABDALA ABDULSATAR</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>ASSINA ABDALA ABDULSATAR</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1274,12 +1279,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1309,17 +1314,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>470</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3918786000010379002</t>
+          <t>3918786000010390006</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1344,7 +1349,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1374,22 +1379,22 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>3918786000010295058</t>
+          <t>3918786000010295010</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1416,17 +1421,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17495</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1456,17 +1461,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>760</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3918786000010367048</t>
+          <t>3918786000010390004</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1491,7 +1496,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1521,22 +1526,22 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>3918786000010295026</t>
+          <t>3918786000010295040</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1563,17 +1568,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1583,7 +1588,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1603,17 +1608,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3918786000010367046</t>
+          <t>3918786000010390002</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1633,17 +1638,12 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Investiu 160 na compra de formas novas</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1658,32 +1658,32 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>3918786000010295054</t>
+          <t>3918786000010295010</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -1715,57 +1715,57 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>550</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3918786000010358004</t>
+          <t>3918786000010380004</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1788,14 +1788,9 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Trabalhar na visibilidade do negócio (fazer um plano de postagem)</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1810,32 +1805,32 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>3918786000010295012</t>
+          <t>3918786000010295044</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -1872,12 +1867,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>10900</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1907,17 +1902,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>11150</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3918786000010358002</t>
+          <t>3918786000010380002</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1972,17 +1967,17 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>3918786000010295052</t>
+          <t>3918786000010295062</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -2019,12 +2014,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2054,17 +2049,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>270</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3918786000010356002</t>
+          <t>3918786000010379008</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2089,7 +2084,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -2104,32 +2099,32 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>3918786000010295090</t>
+          <t>3918786000010295042</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -2166,140 +2161,1326 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>3918786000010379006</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>3918786000010287028</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>3918786000010295056</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>LATIZA AIUBA</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>LATIZA AIUBA</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>10130</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2645</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>6885</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3918786000010379004</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>3918786000010295040</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>8410</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>3918786000010379002</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>3918786000010287026</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>3918786000010295058</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>17495</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>8960</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4670</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>3865</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>3918786000010367048</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>3918786000010295026</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>9125</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1595</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>7430</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>3918786000010367046</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Investiu 160 na compra de formas novas</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>3918786000010295054</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>KHADYA AMADE SILIMO</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>KHADYA AMADE SILIMO</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>3918786000010358004</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>Trabalhar na visibilidade do negócio (fazer um plano de postagem)</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>09-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>3918786000010295012</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>ASSINA ABDALA ABDULSATAR</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>ASSINA ABDALA ABDULSATAR</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>18500</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>5850</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>11150</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>3918786000010358002</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>3918786000010295052</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>JESSICA MARIA JOSE NAMUE</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>JESSICA MARIA JOSE NAMUE</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>3918786000010356002</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>3918786000010287028</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>3918786000010295090</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>TEODORA MANUEL BRAS</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>TEODORA MANUEL BRAS</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>13160</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>3705</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>3918786000004909039</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>1005</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>8450</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>3918786000010353002</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>3918786000004909063</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
         <is>
           <t>08-Jun-2026</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Luisa</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Primeiro Mes de Implementação</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>3918786000010287030</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>3918786000010295028</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr">
+      <c r="AD21" t="inlineStr">
         <is>
           <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
-      <c r="AE13" t="inlineStr">
+      <c r="AE21" t="inlineStr">
         <is>
           <t>Primeira Semana</t>
         </is>
       </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
         <is>
           <t>3918786000007161003</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AI21" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -2566,13 +3747,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CD4CB22-937A-4AD3-8C0C-05205B420FA5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E11E11B-A02D-4B48-986F-BAB168800AF6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{690BED69-35F3-4FCA-9E13-D9C12FB24CD3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B2D074-CB06-454B-80B6-5FDAAF6EB871}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55066A03-7AEC-4FA6-9D71-5E914A78F918}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CC285D4-43DE-4CBC-9F99-49DBE5D481C7}"/>
 </file>
--- a/Financeiro_Report.xlsx
+++ b/Financeiro_Report.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI21"/>
+  <dimension ref="A1:AI37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -539,12 +539,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>620</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -574,17 +574,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>3918786000010395008</t>
+          <t>3918786000010408006</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -604,12 +604,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -624,37 +624,37 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>3918786000010295056</t>
+          <t>3918786000010295036</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -686,12 +686,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>33900</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -721,17 +721,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3918786000010395006</t>
+          <t>3918786000010408004</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -771,32 +771,32 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>3918786000010295018</t>
+          <t>3918786000010295088</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>CATIZA ABAI NURO SITE</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>CATIZA ABAI NURO SITE</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>36000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -868,17 +868,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>35400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3918786000010395004</t>
+          <t>3918786000010408002</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -918,32 +918,32 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>3918786000010295018</t>
+          <t>3918786000010295088</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>CATIZA ABAI NURO SITE</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>CATIZA ABAI NURO SITE</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1015,22 +1015,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-235</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">teve prejuízo na semana porque estava ocupada e nao conseguiu produzir </t>
+          <t>4930</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3918786000010395002</t>
+          <t>3918786000010403026</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1055,7 +1050,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1085,17 +1080,17 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>3918786000010295042</t>
+          <t>3918786000010295052</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>JESSICA MARIA JOSE NAMUE</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>JESSICA MARIA JOSE NAMUE</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1132,12 +1127,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1147,7 +1142,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1167,17 +1162,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>3918786000010390008</t>
+          <t>3918786000010403024</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1202,7 +1197,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1217,32 +1212,32 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>3918786000010295012</t>
+          <t>3918786000010295044</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1279,12 +1274,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>450</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>375</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1314,17 +1309,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>75</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3918786000010390006</t>
+          <t>3918786000010403022</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1349,7 +1344,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1379,17 +1374,17 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>3918786000010295010</t>
+          <t>3918786000010295090</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ARISTINA RABIA JULIO MANUEL</t>
+          <t>TEODORA MANUEL BRAS</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>ARISTINA RABIA JULIO MANUEL</t>
+          <t>TEODORA MANUEL BRAS</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -1421,17 +1416,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>835</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1461,17 +1456,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3918786000010390004</t>
+          <t>3918786000010403020</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1496,7 +1491,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1526,17 +1521,17 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>3918786000010295040</t>
+          <t>3918786000010295062</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -1573,52 +1568,52 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>2955</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3918786000010390002</t>
+          <t>3918786000010403018</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1638,12 +1633,12 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1658,37 +1653,37 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>3918786000010295010</t>
+          <t>3918786000010295054</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>ARISTINA RABIA JULIO MANUEL</t>
+          <t>KHADYA AMADE SILIMO</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>ARISTINA RABIA JULIO MANUEL</t>
+          <t>KHADYA AMADE SILIMO</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1715,17 +1710,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>25175</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1735,7 +1730,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1755,17 +1750,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>18825</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3918786000010380004</t>
+          <t>3918786000010403016</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1788,9 +1783,14 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Investiu uma parte do lucro</t>
+        </is>
+      </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1805,37 +1805,37 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>3918786000010295044</t>
+          <t>3918786000010295036</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>GRACA CHICO PAULO VAGOS</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>GRACA CHICO PAULO VAGOS</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1867,12 +1867,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1902,17 +1902,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>850</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3918786000010380002</t>
+          <t>3918786000010403014</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1952,37 +1952,37 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>3918786000010295062</t>
+          <t>3918786000010295038</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2049,17 +2049,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3918786000010379008</t>
+          <t>3918786000010403012</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -2099,32 +2099,32 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>3918786000010295042</t>
+          <t>3918786000010295038</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>190</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3918786000010379006</t>
+          <t>3918786000010403010</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>3918786000010295056</t>
+          <t>3918786000010295016</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10130</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2343,17 +2343,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>3918786000010379004</t>
+          <t>3918786000010403008</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2408,22 +2408,22 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>3918786000010295040</t>
+          <t>3918786000010295016</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>660</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>870</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>7520</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>3918786000010379002</t>
+          <t>3918786000010403006</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17495</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>240</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,17 +2637,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>520</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>3918786000010367048</t>
+          <t>3918786000010403004</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2744,17 +2744,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2784,17 +2784,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>7430</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>3918786000010367046</t>
+          <t>3918786000010403002</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2814,17 +2814,12 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Investiu 160 na compra de formas novas</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2854,22 +2849,22 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>3918786000010295054</t>
+          <t>3918786000010295028</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2896,57 +2891,57 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>350</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>3918786000010358004</t>
+          <t>3918786000010395008</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2969,14 +2964,9 @@
           <t>Sim</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Trabalhar na visibilidade do negócio (fazer um plano de postagem)</t>
-        </is>
-      </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2991,37 +2981,37 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>3918786000010295012</t>
+          <t>3918786000010295056</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -3053,12 +3043,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>33900</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3088,17 +3078,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>22900</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>11150</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>3918786000010358002</t>
+          <t>3918786000010395006</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3123,7 +3113,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -3153,22 +3143,22 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>3918786000010295052</t>
+          <t>3918786000010295018</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -3200,12 +3190,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3235,17 +3225,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>35400</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>3918786000010356002</t>
+          <t>3918786000010395004</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3285,32 +3275,32 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>3918786000010295090</t>
+          <t>3918786000010295018</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
@@ -3347,140 +3337,2507 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1525</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-235</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">teve prejuízo na semana porque estava ocupada e nao conseguiu produzir </t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>3918786000010395002</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>15-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>3918786000010295042</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>Segunda Semana</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>3918786000010390008</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>15-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>3918786000010295012</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ASSINA ABDALA ABDULSATAR</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>ASSINA ABDALA ABDULSATAR</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>Segunda Semana</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>11750</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1160</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>10120</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>3918786000010390006</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>15-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>3918786000010287026</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>3918786000010295010</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Segunda Semana</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2180</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>3918786000010390004</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>15-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>3918786000010295040</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>Segunda Semana</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>3918786000010390002</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>15-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>3918786000010287026</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>3918786000010295010</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>3918786000010380004</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>3918786000010287026</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>3918786000010295044</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>GRACA CHICO PAULO VAGOS</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>GRACA CHICO PAULO VAGOS</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>10900</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3135</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>7265</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>3918786000010380002</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>3918786000010295062</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>MARAVILHA JANUARIO  CARIA</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>MARAVILHA JANUARIO  CARIA</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>5480</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3530</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1680</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>3918786000010379008</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>09-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>3918786000010295042</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>3918786000010379006</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>3918786000010287028</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>3918786000010295056</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>LATIZA AIUBA</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>LATIZA AIUBA</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>10130</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2645</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>6885</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>3918786000010379004</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>3918786000010295040</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>8410</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>3918786000010379002</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>3918786000010287026</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>3918786000010295058</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>17495</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>8960</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4670</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>3865</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>3918786000010367048</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>3918786000010295026</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>9125</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1595</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>7430</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>3918786000010367046</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Investiu 160 na compra de formas novas</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>3918786000010295054</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>KHADYA AMADE SILIMO</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>KHADYA AMADE SILIMO</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>3918786000010358004</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Trabalhar na visibilidade do negócio (fazer um plano de postagem)</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>09-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>3918786000010295012</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>ASSINA ABDALA ABDULSATAR</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>ASSINA ABDALA ABDULSATAR</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>18500</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>5850</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>11150</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>3918786000010358002</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>3918786000010295052</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>JESSICA MARIA JOSE NAMUE</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>JESSICA MARIA JOSE NAMUE</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>3918786000010356002</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>3918786000010287028</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>3918786000010295090</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>TEODORA MANUEL BRAS</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>TEODORA MANUEL BRAS</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>13160</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>3705</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>3918786000004909039</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>1005</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>8450</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>3918786000010353002</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>3918786000004909063</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
         <is>
           <t>08-Jun-2026</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>Luisa</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>Primeiro Mes de Implementação</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z37" t="inlineStr">
         <is>
           <t>3918786000010287030</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AA37" t="inlineStr">
         <is>
           <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>3918786000010295028</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr">
+      <c r="AD37" t="inlineStr">
         <is>
           <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
-      <c r="AE21" t="inlineStr">
+      <c r="AE37" t="inlineStr">
         <is>
           <t>Primeira Semana</t>
         </is>
       </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
         <is>
           <t>3918786000007161003</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
+      <c r="AI37" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -3747,13 +6104,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E11E11B-A02D-4B48-986F-BAB168800AF6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2669AFD-A6A7-4513-90EA-B57CCB675D35}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B2D074-CB06-454B-80B6-5FDAAF6EB871}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02D3D0F8-03FD-456A-9CB8-EBDE37C5E645}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5CC285D4-43DE-4CBC-9F99-49DBE5D481C7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51819B3A-A689-49E9-A39D-1118DCA4C2E1}"/>
 </file>
--- a/Financeiro_Report.xlsx
+++ b/Financeiro_Report.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI37"/>
+  <dimension ref="A1:AI41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -539,12 +539,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -574,17 +574,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10080</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>3918786000010408006</t>
+          <t>3918786000010445192</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>22-Jun-2026</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -624,37 +624,37 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>3918786000010295036</t>
+          <t>3918786000010295056</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3918786000010408004</t>
+          <t>3918786000010445190</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>22-Jun-2026</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -833,52 +833,52 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>3280</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2975</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>305</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3918786000010408002</t>
+          <t>3918786000010445188</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>22-Jun-2026</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -918,37 +918,37 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>3918786000010295088</t>
+          <t>3918786000010295090</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>SUZANA JOAQUIM VAQUINA</t>
+          <t>TEODORA MANUEL BRAS</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>SUZANA JOAQUIM VAQUINA</t>
+          <t>TEODORA MANUEL BRAS</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1015,17 +1015,22 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Nao produziu durante a semana por motivos de doença</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3918786000010403026</t>
+          <t>3918786000010445186</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1045,12 +1050,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>22-Jun-2026</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1080,22 +1085,22 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>3918786000010295052</t>
+          <t>3918786000010295062</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1127,12 +1132,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>620</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1162,17 +1167,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>3918786000010403024</t>
+          <t>3918786000010408006</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1192,12 +1197,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1212,37 +1217,37 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>3918786000010295044</t>
+          <t>3918786000010295036</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>GRACA CHICO PAULO VAGOS</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>GRACA CHICO PAULO VAGOS</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1274,12 +1279,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1289,7 +1294,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1314,12 +1319,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3918786000010403022</t>
+          <t>3918786000010408004</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1339,12 +1344,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1374,17 +1379,17 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>3918786000010295090</t>
+          <t>3918786000010295088</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -1421,12 +1426,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1436,7 +1441,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1456,17 +1461,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3918786000010403020</t>
+          <t>3918786000010408002</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1486,12 +1491,12 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1506,37 +1511,37 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>3918786000010295062</t>
+          <t>3918786000010295088</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1568,12 +1573,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1603,17 +1608,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3918786000010403018</t>
+          <t>3918786000010403026</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1668,17 +1673,17 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>3918786000010295054</t>
+          <t>3918786000010295052</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>JESSICA MARIA JOSE NAMUE</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>JESSICA MARIA JOSE NAMUE</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -1710,84 +1715,79 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>3918786000010403024</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>25175</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1880</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4470</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>18825</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>3918786000010403016</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Investiu uma parte do lucro</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
           <t>17-Jun-2026</t>
@@ -1805,32 +1805,32 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>3918786000010295036</t>
+          <t>3918786000010295044</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -1867,12 +1867,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>450</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>375</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>75</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3918786000010403014</t>
+          <t>3918786000010403022</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1967,17 +1967,17 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>3918786000010295038</t>
+          <t>3918786000010295090</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>FRANCISCA LUCIANO BOMES</t>
+          <t>TEODORA MANUEL BRAS</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>FRANCISCA LUCIANO BOMES</t>
+          <t>TEODORA MANUEL BRAS</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>835</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2049,17 +2049,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3918786000010403012</t>
+          <t>3918786000010403020</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2099,37 +2099,37 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>3918786000010295038</t>
+          <t>3918786000010295062</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>FRANCISCA LUCIANO BOMES</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>FRANCISCA LUCIANO BOMES</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3918786000010403010</t>
+          <t>3918786000010403018</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2261,22 +2261,22 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>3918786000010295016</t>
+          <t>3918786000010295054</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t>KHADYA AMADE SILIMO</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t>KHADYA AMADE SILIMO</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2303,17 +2303,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>25175</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2343,17 +2343,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>18825</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>3918786000010403008</t>
+          <t>3918786000010403016</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2373,7 +2373,12 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>Investiu uma parte do lucro</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -2408,17 +2413,17 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>3918786000010295016</t>
+          <t>3918786000010295036</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
@@ -2455,12 +2460,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2490,17 +2495,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>850</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>3918786000010403006</t>
+          <t>3918786000010403014</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2555,17 +2560,17 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>3918786000010295058</t>
+          <t>3918786000010295038</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -2602,12 +2607,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,17 +2642,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>3918786000010403004</t>
+          <t>3918786000010403012</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2672,7 +2677,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2687,37 +2692,37 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>3918786000010295026</t>
+          <t>3918786000010295038</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2749,7 +2754,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2764,7 +2769,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2784,17 +2789,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>190</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>3918786000010403002</t>
+          <t>3918786000010403010</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2814,12 +2819,12 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2849,22 +2854,22 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>3918786000010295028</t>
+          <t>3918786000010295016</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>ESMERALDA JORGE MURIRIUA</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>ESMERALDA JORGE MURIRIUA</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2896,12 +2901,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2931,17 +2936,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>3918786000010395008</t>
+          <t>3918786000010403008</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2961,12 +2966,12 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2981,32 +2986,32 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>3918786000010295056</t>
+          <t>3918786000010295016</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
@@ -3043,12 +3048,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>33900</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>660</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3078,17 +3083,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>870</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>10500</t>
+          <t>7520</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>3918786000010395006</t>
+          <t>3918786000010403006</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3113,7 +3118,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -3128,32 +3133,32 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>3918786000010295018</t>
+          <t>3918786000010295058</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>CATIZA ABAI NURO SITE</t>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>CATIZA ABAI NURO SITE</t>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
@@ -3190,12 +3195,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>36000</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>240</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3225,17 +3230,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>520</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>35400</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>3918786000010395004</t>
+          <t>3918786000010403004</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3260,7 +3265,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -3290,22 +3295,22 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>3918786000010295018</t>
+          <t>3918786000010295026</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>CATIZA ABAI NURO SITE</t>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>CATIZA ABAI NURO SITE</t>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -3337,12 +3342,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3352,7 +3357,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3372,22 +3377,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-235</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">teve prejuízo na semana porque estava ocupada e nao conseguiu produzir </t>
+          <t>1390</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>3918786000010395002</t>
+          <t>3918786000010403002</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -3442,17 +3442,17 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>3918786000010295042</t>
+          <t>3918786000010295028</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>350</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>350</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>3918786000010390008</t>
+          <t>3918786000010395008</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3574,32 +3574,32 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>3918786000010295012</t>
+          <t>3918786000010295056</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>33900</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>22900</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>3918786000010390006</t>
+          <t>3918786000010395006</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3721,32 +3721,32 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>3918786000010295010</t>
+          <t>3918786000010295018</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>ARISTINA RABIA JULIO MANUEL</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>ARISTINA RABIA JULIO MANUEL</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
@@ -3778,82 +3778,82 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>36000</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2180</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1320</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>35400</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>3918786000010395004</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>760</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>3918786000010390004</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -3883,22 +3883,22 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>3918786000010295040</t>
+          <t>3918786000010295018</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3965,17 +3965,22 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-235</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">teve prejuízo na semana porque estava ocupada e nao conseguiu produzir </t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>3918786000010390002</t>
+          <t>3918786000010395002</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3995,7 +4000,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -4015,37 +4020,37 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>3918786000010295010</t>
+          <t>3918786000010295042</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ARISTINA RABIA JULIO MANUEL</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>ARISTINA RABIA JULIO MANUEL</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -4077,12 +4082,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>600</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4092,7 +4097,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4112,17 +4117,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>90</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>3918786000010380004</t>
+          <t>3918786000010390008</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -4147,7 +4152,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -4162,37 +4167,37 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>3918786000010295044</t>
+          <t>3918786000010295012</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>GRACA CHICO PAULO VAGOS</t>
+          <t>ASSINA ABDALA ABDULSATAR</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>GRACA CHICO PAULO VAGOS</t>
+          <t>ASSINA ABDALA ABDULSATAR</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -4224,12 +4229,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4259,17 +4264,17 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>470</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>3918786000010380002</t>
+          <t>3918786000010390006</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4294,7 +4299,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -4309,37 +4314,37 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>3918786000010295062</t>
+          <t>3918786000010295010</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -4366,17 +4371,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4406,17 +4411,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>760</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>3918786000010379008</t>
+          <t>3918786000010390004</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4441,7 +4446,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -4471,22 +4476,22 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>3918786000010295042</t>
+          <t>3918786000010295040</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -4518,7 +4523,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4533,7 +4538,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4558,12 +4563,12 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3918786000010379006</t>
+          <t>3918786000010390002</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4583,12 +4588,12 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -4603,32 +4608,32 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>3918786000010295056</t>
+          <t>3918786000010295010</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
@@ -4665,12 +4670,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>10130</t>
+          <t>550</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4680,59 +4685,59 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>3918786000010380004</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>6885</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>3918786000010379004</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
       <c r="T30" t="inlineStr">
         <is>
           <t>08-Jun-2026</t>
@@ -4750,32 +4755,32 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>3918786000010295040</t>
+          <t>3918786000010295044</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
@@ -4812,12 +4817,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>10900</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4847,17 +4852,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>3918786000010379002</t>
+          <t>3918786000010380002</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4897,32 +4902,32 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>3918786000010295058</t>
+          <t>3918786000010295062</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
@@ -4959,12 +4964,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17495</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4994,17 +4999,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>270</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>3918786000010367048</t>
+          <t>3918786000010379008</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -5029,7 +5034,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -5059,17 +5064,17 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>3918786000010295026</t>
+          <t>3918786000010295042</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
@@ -5101,84 +5106,79 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>9125</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1595</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>3918786000010379006</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>7430</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>3918786000010367046</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>Investiu 160 na compra de formas novas</t>
-        </is>
-      </c>
       <c r="T33" t="inlineStr">
         <is>
           <t>08-Jun-2026</t>
@@ -5196,32 +5196,32 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>3918786000010295054</t>
+          <t>3918786000010295056</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
@@ -5253,87 +5253,82 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>10130</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2645</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>6885</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>3918786000010379004</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>3918786000010358004</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>Trabalhar na visibilidade do negócio (fazer um plano de postagem)</t>
-        </is>
-      </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -5363,17 +5358,17 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>3918786000010295012</t>
+          <t>3918786000010295040</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
@@ -5410,12 +5405,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5445,17 +5440,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>490</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>11150</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3918786000010358002</t>
+          <t>3918786000010379002</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5495,32 +5490,32 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>3918786000010295052</t>
+          <t>3918786000010295058</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
@@ -5557,12 +5552,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>17495</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>8960</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5592,17 +5587,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>3918786000010356002</t>
+          <t>3918786000010367048</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5642,32 +5637,32 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>3918786000010295090</t>
+          <t>3918786000010295026</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
@@ -5699,145 +5694,743 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>9125</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1595</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>7430</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>3918786000010367046</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Investiu 160 na compra de formas novas</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>3918786000010295054</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>KHADYA AMADE SILIMO</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>KHADYA AMADE SILIMO</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>3918786000010358004</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Trabalhar na visibilidade do negócio (fazer um plano de postagem)</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>09-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>3918786000010295012</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>ASSINA ABDALA ABDULSATAR</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>ASSINA ABDALA ABDULSATAR</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>18500</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>5850</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>11150</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>3918786000010358002</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>3918786000010295052</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>JESSICA MARIA JOSE NAMUE</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>JESSICA MARIA JOSE NAMUE</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>3918786000010356002</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>3918786000010287028</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>3918786000010295090</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>TEODORA MANUEL BRAS</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>TEODORA MANUEL BRAS</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>13160</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>3705</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>3918786000004909039</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>1005</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>8450</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>3918786000010353002</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>3918786000004909063</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>08-Jun-2026</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>Luisa</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>Primeiro Mes de Implementação</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>3918786000010287030</t>
         </is>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>3918786000010295028</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
-      <c r="AD37" t="inlineStr">
+      <c r="AD41" t="inlineStr">
         <is>
           <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
-      <c r="AE37" t="inlineStr">
+      <c r="AE41" t="inlineStr">
         <is>
           <t>Primeira Semana</t>
         </is>
       </c>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AG37" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AH37" t="inlineStr">
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
         <is>
           <t>3918786000007161003</t>
         </is>
       </c>
-      <c r="AI37" t="inlineStr">
+      <c r="AI41" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -6104,13 +6697,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2669AFD-A6A7-4513-90EA-B57CCB675D35}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{750C6DC3-5441-420E-9648-8B552DE0A933}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02D3D0F8-03FD-456A-9CB8-EBDE37C5E645}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B9C1D3D-462B-41FC-80FF-BCC847B4CCC5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51819B3A-A689-49E9-A39D-1118DCA4C2E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61FC7D6D-BE92-4477-A130-8626FE27164A}"/>
 </file>
--- a/Financeiro_Report.xlsx
+++ b/Financeiro_Report.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI41"/>
+  <dimension ref="A1:AI58"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -539,12 +539,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>13650</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>640</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -574,17 +574,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>3918786000010445192</t>
+          <t>3918786000010516002</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -604,12 +604,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>29-Jun-2026</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -624,37 +624,37 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>3918786000010295056</t>
+          <t>3918786000010295058</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>Terceira Semana</t>
+          <t>Quarta Semana</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -729,9 +729,14 @@
           <t>0</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Nao produziu na semana por motivos de doença</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3918786000010445190</t>
+          <t>3918786000010502011</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -756,7 +761,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>29-Jun-2026</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -766,7 +771,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Primeiro Mes de Implementação</t>
+          <t>Quarto Mes de Implementação</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -786,22 +791,22 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>3918786000010295088</t>
+          <t>3918786000010295010</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>SUZANA JOAQUIM VAQUINA</t>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>SUZANA JOAQUIM VAQUINA</t>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Terceira Semana</t>
+          <t>Quarta Semana</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -833,12 +838,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>700</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -873,12 +878,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>700</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3918786000010445188</t>
+          <t>3918786000010478026</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -898,12 +903,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -918,32 +923,32 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>3918786000010295090</t>
+          <t>3918786000010295036</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1025,12 +1030,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Nao produziu durante a semana por motivos de doença</t>
+          <t>lucro zero (esta no período de criação de frangos)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3918786000010445186</t>
+          <t>3918786000010478024</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1055,7 +1060,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1085,17 +1090,17 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>3918786000010295062</t>
+          <t>3918786000010295018</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -1132,12 +1137,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>610</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1167,17 +1172,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10080</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>3918786000010408006</t>
+          <t>3918786000010478022</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1197,12 +1202,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1217,37 +1222,37 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>3918786000010295036</t>
+          <t>3918786000010295058</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1279,52 +1284,52 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3918786000010408004</t>
+          <t>3918786000010478020</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1349,7 +1354,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1364,37 +1369,37 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>3918786000010295088</t>
+          <t>3918786000010295016</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>SUZANA JOAQUIM VAQUINA</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>SUZANA JOAQUIM VAQUINA</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1426,12 +1431,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10056</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1441,7 +1446,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1461,17 +1466,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3918786000010408002</t>
+          <t>3918786000010478018</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1496,7 +1501,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1511,37 +1516,37 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>3918786000010295088</t>
+          <t>3918786000010295054</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>SUZANA JOAQUIM VAQUINA</t>
+          <t>KHADYA AMADE SILIMO</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>SUZANA JOAQUIM VAQUINA</t>
+          <t>KHADYA AMADE SILIMO</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1573,12 +1578,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>900</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1608,17 +1613,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3918786000010403026</t>
+          <t>3918786000010478016</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1643,7 +1648,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1658,37 +1663,37 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>3918786000010295052</t>
+          <t>3918786000010295038</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1720,12 +1725,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1735,7 +1740,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1755,17 +1760,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3918786000010403024</t>
+          <t>3918786000010478014</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1790,7 +1795,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1805,37 +1810,37 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>3918786000010295044</t>
+          <t>3918786000010295052</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>GRACA CHICO PAULO VAGOS</t>
+          <t>JESSICA MARIA JOSE NAMUE</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>GRACA CHICO PAULO VAGOS</t>
+          <t>JESSICA MARIA JOSE NAMUE</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1867,12 +1872,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1902,17 +1907,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3918786000010403022</t>
+          <t>3918786000010478012</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1937,7 +1942,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1952,37 +1957,37 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>3918786000010295090</t>
+          <t>3918786000010295042</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -2009,17 +2014,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2049,17 +2054,22 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2645</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Investiu 500 em formas para testar um novo servico</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3918786000010403020</t>
+          <t>3918786000010478010</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2079,12 +2089,12 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -2114,22 +2124,22 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>3918786000010295062</t>
+          <t>3918786000010295026</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -2161,12 +2171,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>200</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2176,62 +2186,62 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>3918786000010478008</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>1735</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>3918786000010403018</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -2261,22 +2271,22 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>3918786000010295054</t>
+          <t>3918786000010295012</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>ASSINA ABDALA ABDULSATAR</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>ASSINA ABDALA ABDULSATAR</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2303,17 +2313,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25175</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2323,7 +2333,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2343,17 +2353,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18825</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>3918786000010403016</t>
+          <t>3918786000010478006</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2373,17 +2383,12 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Investiu uma parte do lucro</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2413,22 +2418,22 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>3918786000010295036</t>
+          <t>3918786000010295024</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t>DULQUIFAL ASSANE SIMBA</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t>DULQUIFAL ASSANE SIMBA</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2460,12 +2465,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2475,7 +2480,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2500,12 +2505,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>3918786000010403014</t>
+          <t>3918786000010478004</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2525,12 +2530,12 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2545,32 +2550,32 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>3918786000010295038</t>
+          <t>3918786000010295024</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>FRANCISCA LUCIANO BOMES</t>
+          <t>DULQUIFAL ASSANE SIMBA</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>FRANCISCA LUCIANO BOMES</t>
+          <t>DULQUIFAL ASSANE SIMBA</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
@@ -2607,7 +2612,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2622,7 +2627,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2647,12 +2652,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>3918786000010403012</t>
+          <t>3918786000010478002</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2672,12 +2677,12 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2692,32 +2697,32 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>3918786000010295038</t>
+          <t>3918786000010295024</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>FRANCISCA LUCIANO BOMES</t>
+          <t>DULQUIFAL ASSANE SIMBA</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>FRANCISCA LUCIANO BOMES</t>
+          <t>DULQUIFAL ASSANE SIMBA</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
@@ -2754,12 +2759,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2769,7 +2774,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2789,17 +2794,22 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>nao produziu durante a semana porque estava doente</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>3918786000010403010</t>
+          <t>3918786000010471004</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2819,12 +2829,12 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2839,37 +2849,37 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>3918786000010295016</t>
+          <t>3918786000010295010</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2901,12 +2911,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2916,7 +2926,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2936,17 +2946,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>3918786000010403008</t>
+          <t>3918786000010471002</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2971,7 +2981,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2986,37 +2996,37 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>3918786000010295016</t>
+          <t>3918786000010295044</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -3048,12 +3058,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3063,7 +3073,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3083,17 +3093,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>3918786000010403006</t>
+          <t>3918786000010445192</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3113,12 +3123,12 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>22-Jun-2026</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -3133,37 +3143,37 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>3918786000010295058</t>
+          <t>3918786000010295056</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -3195,12 +3205,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3210,7 +3220,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3230,17 +3240,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>3918786000010403004</t>
+          <t>3918786000010445190</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3260,12 +3270,12 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>22-Jun-2026</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -3280,37 +3290,37 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>3918786000010295026</t>
+          <t>3918786000010295088</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -3342,12 +3352,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3377,17 +3387,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>305</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>3918786000010403002</t>
+          <t>3918786000010445188</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3407,12 +3417,12 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>22-Jun-2026</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -3427,37 +3437,37 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>3918786000010295028</t>
+          <t>3918786000010295090</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>ESMERALDA JORGE MURIRIUA</t>
+          <t>TEODORA MANUEL BRAS</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>ESMERALDA JORGE MURIRIUA</t>
+          <t>TEODORA MANUEL BRAS</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -3489,7 +3499,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3504,7 +3514,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3529,12 +3539,17 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Nao produziu durante a semana por motivos de doença</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>3918786000010395008</t>
+          <t>3918786000010445186</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3554,12 +3569,12 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>22-Jun-2026</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -3574,37 +3589,37 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>3918786000010295056</t>
+          <t>3918786000010295062</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3636,12 +3651,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>33900</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>620</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3651,7 +3666,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3671,17 +3686,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>10500</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>3918786000010395006</t>
+          <t>3918786000010408006</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3701,12 +3716,12 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -3736,22 +3751,22 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>3918786000010295018</t>
+          <t>3918786000010295036</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>CATIZA ABAI NURO SITE</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>CATIZA ABAI NURO SITE</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3783,7 +3798,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>36000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3798,7 +3813,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3818,17 +3833,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>35400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>3918786000010395004</t>
+          <t>3918786000010408004</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3848,12 +3863,12 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -3868,37 +3883,37 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>3918786000010295018</t>
+          <t>3918786000010295088</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>CATIZA ABAI NURO SITE</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>CATIZA ABAI NURO SITE</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3930,12 +3945,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3945,7 +3960,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3965,22 +3980,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-235</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">teve prejuízo na semana porque estava ocupada e nao conseguiu produzir </t>
+          <t>0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>3918786000010395002</t>
+          <t>3918786000010408002</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -4000,12 +4010,12 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -4020,37 +4030,37 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>3918786000010295042</t>
+          <t>3918786000010295088</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -4082,77 +4092,77 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>6850</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>600</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>4930</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>3918786000010403026</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>3918786000010390008</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -4182,17 +4192,17 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>3918786000010295012</t>
+          <t>3918786000010295052</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>JESSICA MARIA JOSE NAMUE</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>JESSICA MARIA JOSE NAMUE</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
@@ -4229,12 +4239,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4244,62 +4254,62 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>3918786000010403024</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>10120</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>3918786000010390006</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -4329,17 +4339,17 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>3918786000010295010</t>
+          <t>3918786000010295044</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ARISTINA RABIA JULIO MANUEL</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>ARISTINA RABIA JULIO MANUEL</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
@@ -4371,82 +4381,82 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2180</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1320</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>3918786000010403022</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>760</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>3918786000010390004</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -4461,32 +4471,32 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>3918786000010295040</t>
+          <t>3918786000010295090</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>TEODORA MANUEL BRAS</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>TEODORA MANUEL BRAS</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
@@ -4523,12 +4533,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>835</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4538,7 +4548,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4558,17 +4568,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3918786000010390002</t>
+          <t>3918786000010403020</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4588,12 +4598,12 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -4608,37 +4618,37 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>3918786000010295010</t>
+          <t>3918786000010295062</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>ARISTINA RABIA JULIO MANUEL</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>ARISTINA RABIA JULIO MANUEL</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -4670,52 +4680,52 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3918786000010380004</t>
+          <t>3918786000010403018</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4740,7 +4750,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -4755,37 +4765,37 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>3918786000010295044</t>
+          <t>3918786000010295054</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>GRACA CHICO PAULO VAGOS</t>
+          <t>KHADYA AMADE SILIMO</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>GRACA CHICO PAULO VAGOS</t>
+          <t>KHADYA AMADE SILIMO</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -4812,17 +4822,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>25175</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4852,17 +4862,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>18825</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>3918786000010380002</t>
+          <t>3918786000010403016</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4885,9 +4895,14 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Investiu uma parte do lucro</t>
+        </is>
+      </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -4917,22 +4932,22 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>3918786000010295062</t>
+          <t>3918786000010295036</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -4964,12 +4979,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4999,17 +5014,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>850</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>3918786000010379008</t>
+          <t>3918786000010403014</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -5034,7 +5049,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -5049,37 +5064,37 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>3918786000010295042</t>
+          <t>3918786000010295038</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -5111,7 +5126,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5151,12 +5166,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>3918786000010379006</t>
+          <t>3918786000010403012</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5181,7 +5196,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -5196,32 +5211,32 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>3918786000010295056</t>
+          <t>3918786000010295038</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
@@ -5258,12 +5273,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>10130</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5293,17 +5308,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>190</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>3918786000010379004</t>
+          <t>3918786000010403010</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5328,7 +5343,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -5358,17 +5373,17 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>3918786000010295040</t>
+          <t>3918786000010295016</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
@@ -5405,12 +5420,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5440,17 +5455,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3918786000010379002</t>
+          <t>3918786000010403008</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5470,12 +5485,12 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -5490,37 +5505,37 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>3918786000010295058</t>
+          <t>3918786000010295016</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -5552,12 +5567,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17495</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>660</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5587,17 +5602,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>870</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>7520</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>3918786000010367048</t>
+          <t>3918786000010403006</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5622,7 +5637,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -5637,37 +5652,37 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>3918786000010295026</t>
+          <t>3918786000010295058</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -5694,87 +5709,82 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>4985</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>9125</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1595</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>4225</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>3918786000010403004</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>7430</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>3918786000010367046</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>Investiu 160 na compra de formas novas</t>
-        </is>
-      </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -5804,22 +5814,22 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>3918786000010295054</t>
+          <t>3918786000010295026</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -5846,17 +5856,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5866,7 +5876,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -5886,17 +5896,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>3918786000010358004</t>
+          <t>3918786000010403002</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5916,17 +5926,12 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>Trabalhar na visibilidade do negócio (fazer um plano de postagem)</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -5956,22 +5961,22 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>3918786000010295012</t>
+          <t>3918786000010295028</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -6003,12 +6008,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>350</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6038,17 +6043,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>11150</t>
+          <t>350</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>3918786000010358002</t>
+          <t>3918786000010395008</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -6073,7 +6078,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -6088,37 +6093,37 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>3918786000010295052</t>
+          <t>3918786000010295056</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -6150,12 +6155,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>33900</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6185,17 +6190,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>22900</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>3918786000010356002</t>
+          <t>3918786000010395006</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -6220,7 +6225,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -6235,37 +6240,37 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>3918786000010295090</t>
+          <t>3918786000010295018</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -6297,140 +6302,2654 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>36000</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>35400</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>3918786000010395004</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>3918786000010295018</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>CATIZA ABAI NURO SITE</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>CATIZA ABAI NURO SITE</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1525</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>-235</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">teve prejuízo na semana porque estava ocupada e nao conseguiu produzir </t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>3918786000010395002</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>15-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>3918786000010295042</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>Segunda Semana</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>3918786000010390008</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>15-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>3918786000010295012</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>ASSINA ABDALA ABDULSATAR</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>ASSINA ABDALA ABDULSATAR</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>Segunda Semana</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>11750</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1160</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>470</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>10120</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>3918786000010390006</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>15-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>3918786000010287026</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>3918786000010295010</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>Segunda Semana</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2180</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1320</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>760</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>3918786000010390004</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>15-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>3918786000010295040</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>Segunda Semana</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3918786000010390002</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>15-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>3918786000010287026</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>3918786000010295010</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>3918786000010380004</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>3918786000010287026</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>3918786000010295044</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>GRACA CHICO PAULO VAGOS</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>GRACA CHICO PAULO VAGOS</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>10900</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>3135</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>7265</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>3918786000010380002</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>3918786000010295062</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>MARAVILHA JANUARIO  CARIA</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>MARAVILHA JANUARIO  CARIA</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>5480</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>3530</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1680</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>3918786000010379008</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>09-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>3918786000010295042</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>3918786000010379006</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>3918786000010287028</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>3918786000010295056</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>LATIZA AIUBA</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>LATIZA AIUBA</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>10130</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2645</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>6885</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>3918786000010379004</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>3918786000010295040</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>8410</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>3918786000010379002</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>3918786000010287026</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>3918786000010295058</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>17495</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>8960</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4670</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>3865</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>3918786000010367048</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>3918786000010295026</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>9125</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1595</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>7430</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>3918786000010367046</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Investiu 160 na compra de formas novas</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>3918786000010295054</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>KHADYA AMADE SILIMO</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>KHADYA AMADE SILIMO</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>3918786000010358004</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Trabalhar na visibilidade do negócio (fazer um plano de postagem)</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>09-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>3918786000010295012</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>ASSINA ABDALA ABDULSATAR</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>ASSINA ABDALA ABDULSATAR</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>18500</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>5850</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>11150</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>3918786000010358002</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>3918786000010295052</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>JESSICA MARIA JOSE NAMUE</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>JESSICA MARIA JOSE NAMUE</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>3918786000010356002</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>3918786000010287028</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>3918786000010295090</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>TEODORA MANUEL BRAS</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>TEODORA MANUEL BRAS</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>13160</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>3705</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
         <is>
           <t>3918786000004909039</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
         <is>
           <t>1005</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>8450</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>3918786000010353002</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>3918786000004909063</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>08-Jun-2026</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>Luisa</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>Primeiro Mes de Implementação</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>3918786000010287030</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AA58" t="inlineStr">
         <is>
           <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>3918786000010295028</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
+      <c r="AC58" t="inlineStr">
         <is>
           <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
-      <c r="AD41" t="inlineStr">
+      <c r="AD58" t="inlineStr">
         <is>
           <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
-      <c r="AE41" t="inlineStr">
+      <c r="AE58" t="inlineStr">
         <is>
           <t>Primeira Semana</t>
         </is>
       </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AG41" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AH41" t="inlineStr">
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
         <is>
           <t>3918786000007161003</t>
         </is>
       </c>
-      <c r="AI41" t="inlineStr">
+      <c r="AI58" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -6697,13 +9216,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{750C6DC3-5441-420E-9648-8B552DE0A933}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85B09157-03A8-41C7-98E9-7C229E3B7D27}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B9C1D3D-462B-41FC-80FF-BCC847B4CCC5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42F7F794-6DCF-426F-897B-875D1195F2A0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61FC7D6D-BE92-4477-A130-8626FE27164A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EB1116B-1FAF-4E63-A1D5-D68AD683F818}"/>
 </file>
--- a/Financeiro_Report.xlsx
+++ b/Financeiro_Report.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AI95"/>
+  <dimension ref="A1:AI97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -532,14 +532,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,64 +547,64 @@
           <t>true</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nao Produziu durante a semana porque teve infelicidade </t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>3918786000010601007</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2910</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>3918786000010591020</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -639,17 +634,17 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>3918786000010295026</t>
+          <t>3918786000010295036</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -679,14 +674,9 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -699,11 +689,6 @@
           <t>true</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>PAM VERDE</t>
@@ -721,17 +706,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>-3000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3918786000010591018</t>
+          <t>3918786000010601005</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -756,7 +741,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>08-Jul-2026</t>
+          <t>09-Jul-2026</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -766,42 +751,42 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Primeiro Mes de Implementação</t>
+          <t>Segundo Mes de Implementação</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>3918786000010295044</t>
+          <t>3918786000010295018</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>GRACA CHICO PAULO VAGOS</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>GRACA CHICO PAULO VAGOS</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>Quarta Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -833,12 +818,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -873,12 +858,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>3918786000010591016</t>
+          <t>3918786000010591020</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -913,47 +898,47 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Segundo Mes de Implementação</t>
+          <t>Primeiro Mes de Implementação</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>3918786000010295090</t>
+          <t>3918786000010295026</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Quarta Semana</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -980,12 +965,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>400</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -995,7 +980,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1020,12 +1005,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>400</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>3918786000010591014</t>
+          <t>3918786000010591018</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1045,7 +1030,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1060,7 +1045,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Segundo Mes de Implementação</t>
+          <t>Primeiro Mes de Implementação</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1095,7 +1080,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Quarta Semana</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1127,12 +1112,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9900</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1162,17 +1147,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2255</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>3918786000010591012</t>
+          <t>3918786000010591016</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1212,32 +1197,32 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>3918786000010295028</t>
+          <t>3918786000010295090</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>ESMERALDA JORGE MURIRIUA</t>
+          <t>TEODORA MANUEL BRAS</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>ESMERALDA JORGE MURIRIUA</t>
+          <t>TEODORA MANUEL BRAS</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -1247,7 +1232,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1267,54 +1252,59 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>150</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>3918786000010591010</t>
+          <t>3918786000010591014</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1349,42 +1339,42 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Primeiro Mes de Implementação</t>
+          <t>Segundo Mes de Implementação</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>3918786000010295028</t>
+          <t>3918786000010295044</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>ESMERALDA JORGE MURIRIUA</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>ESMERALDA JORGE MURIRIUA</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>Quarta Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1416,12 +1406,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8790</t>
+          <t>9900</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1451,17 +1441,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>2255</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3918786000010591008</t>
+          <t>3918786000010591012</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1496,7 +1486,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Primeiro Mes de Implementação</t>
+          <t>Segundo Mes de Implementação</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1531,7 +1521,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>Terceira Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1556,19 +1546,14 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1598,17 +1583,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>8180</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3918786000010591006</t>
+          <t>3918786000010591010</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1628,7 +1613,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1643,42 +1628,42 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Segundo Mes de Implementação</t>
+          <t>Primeiro Mes de Implementação</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>3918786000010295036</t>
+          <t>3918786000010295028</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Quarta Semana</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1710,12 +1695,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14850</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1745,17 +1730,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>700</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>6490</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3918786000010591004</t>
+          <t>3918786000010591008</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1790,42 +1775,42 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Segundo Mes de Implementação</t>
+          <t>Primeiro Mes de Implementação</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>3918786000010295058</t>
+          <t>3918786000010295028</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1857,12 +1842,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>8700</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>320</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1872,7 +1857,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1892,17 +1877,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>8180</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>3918786000010591002</t>
+          <t>3918786000010591006</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1922,7 +1907,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1942,32 +1927,32 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>3918786000010295012</t>
+          <t>3918786000010295036</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -1977,7 +1962,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -2004,12 +1989,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>14850</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2039,17 +2024,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>11440</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3918786000010577014</t>
+          <t>3918786000010591004</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2074,52 +2059,52 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Azarias</t>
+          <t>Luisa</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Primeiro Mes de Implementação</t>
+          <t>Segundo Mes de Implementação</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>3918786000010295004</t>
+          <t>3918786000010295058</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>ANCHA FRANCISCO LIMA</t>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>ANCHA FRANCISCO LIMA</t>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>Terceira Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -2151,12 +2136,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>550</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2186,17 +2171,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>350</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3918786000010577012</t>
+          <t>3918786000010591002</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2221,57 +2206,57 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>08-Jul-2026</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Azarias</t>
+          <t>Luisa</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Primeiro Mes de Implementação</t>
+          <t>Segundo Mes de Implementação</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>3918786000010295004</t>
+          <t>3918786000010295012</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ANCHA FRANCISCO LIMA</t>
+          <t>ASSINA ABDALA ABDULSATAR</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>ANCHA FRANCISCO LIMA</t>
+          <t>ASSINA ABDALA ABDULSATAR</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -2298,12 +2283,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>200</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2333,17 +2318,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>3918786000010577010</t>
+          <t>3918786000010577014</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2368,7 +2353,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>22-Jun-2026</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -2413,7 +2398,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2445,12 +2430,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17970</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>200</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2480,17 +2465,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>480</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>17345</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>3918786000010577008</t>
+          <t>3918786000010577012</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2515,7 +2500,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>01-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2530,37 +2515,37 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>3918786000010295074</t>
+          <t>3918786000010295004</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>OLINDA CARLINDO NAMIRECA</t>
+          <t>ANCHA FRANCISCO LIMA</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>OLINDA CARLINDO NAMIRECA</t>
+          <t>ANCHA FRANCISCO LIMA</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2592,12 +2577,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>6200</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2632,12 +2617,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>3918786000010575018</t>
+          <t>3918786000010577010</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2662,17 +2647,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>06-Jul-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>Azarias</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Segundo Mes de Implementação</t>
+          <t>Primeiro Mes de Implementação</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2692,17 +2677,17 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>3918786000010295056</t>
+          <t>3918786000010295004</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>ANCHA FRANCISCO LIMA</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>ANCHA FRANCISCO LIMA</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
@@ -2739,82 +2724,82 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>17970</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>17345</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>3918786000010577008</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>1220</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>3918786000010575016</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>06-Jul-2026</t>
+          <t>01-Jun-2026</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Luisa</t>
+          <t>Azarias</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2824,37 +2809,37 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>3918786000010295056</t>
+          <t>3918786000010295074</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>OLINDA CARLINDO NAMIRECA</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>OLINDA CARLINDO NAMIRECA</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>Quarta Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2886,12 +2871,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>960</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2921,17 +2906,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>3918786000010575014</t>
+          <t>3918786000010575018</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2971,32 +2956,32 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>3918786000010295062</t>
+          <t>3918786000010295056</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
@@ -3006,7 +2991,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -3033,12 +3018,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3068,17 +3053,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>3918786000010575012</t>
+          <t>3918786000010575016</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3098,7 +3083,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -3113,42 +3098,42 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Segundo Mes de Implementação</t>
+          <t>Primeiro Mes de Implementação</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>3918786000010295042</t>
+          <t>3918786000010295056</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Quarta Semana</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -3225,7 +3210,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>3918786000010575010</t>
+          <t>3918786000010575014</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3265,32 +3250,32 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>3918786000010295088</t>
+          <t>3918786000010295062</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>SUZANA JOAQUIM VAQUINA</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>SUZANA JOAQUIM VAQUINA</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
@@ -3300,7 +3285,7 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -3372,7 +3357,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>3918786000010575008</t>
+          <t>3918786000010575012</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3392,7 +3377,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -3427,17 +3412,17 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>3918786000010295024</t>
+          <t>3918786000010295042</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>DULQUIFAL ASSANE SIMBA</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>DULQUIFAL ASSANE SIMBA</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
@@ -3447,7 +3432,7 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -3474,12 +3459,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>46020</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3509,17 +3494,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>29125</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>3918786000010575006</t>
+          <t>3918786000010575010</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3554,42 +3539,42 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Primeiro Mes de Implementação</t>
+          <t>Segundo Mes de Implementação</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>3918786000010295040</t>
+          <t>3918786000010295088</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>Quarta Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3621,12 +3606,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3656,17 +3641,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>3918786000010575004</t>
+          <t>3918786000010575008</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3686,7 +3671,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -3706,32 +3691,32 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>3918786000010295040</t>
+          <t>3918786000010295024</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>DULQUIFAL ASSANE SIMBA</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>DULQUIFAL ASSANE SIMBA</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
@@ -3768,12 +3753,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>46020</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3783,7 +3768,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3803,17 +3788,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3940</t>
+          <t>29125</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>3918786000010575002</t>
+          <t>3918786000010575006</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3883,7 +3868,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>Terceira Semana</t>
+          <t>Quarta Semana</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3915,12 +3900,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>765</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3950,17 +3935,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>3918786000010573020</t>
+          <t>3918786000010575004</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3985,7 +3970,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -4000,32 +3985,32 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>3918786000010295054</t>
+          <t>3918786000010295040</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
@@ -4035,7 +4020,7 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
@@ -4062,12 +4047,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>970</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4077,77 +4062,62 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>3940</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>3918786000010575002</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>4625</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>15-Jun-2026</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>3918786000010573018</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>07-Jul-2026</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Passou a comprar num fornecedor mais proximo, reduzindo assim a emissao de pegada de carbono</t>
+          <t>06-Jul-2026</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -4160,11 +4130,6 @@
           <t>Primeiro Mes de Implementação</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="Y26" t="inlineStr">
         <is>
           <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
@@ -4182,27 +4147,27 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>3918786000010295054</t>
+          <t>3918786000010295040</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>Quarta Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
@@ -4224,84 +4189,79 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1650</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>5625</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>3918786000010573020</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>4685</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>3918786000010573016</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>Investiu 1640</t>
-        </is>
-      </c>
       <c r="T27" t="inlineStr">
         <is>
           <t>07-Jul-2026</t>
@@ -4334,17 +4294,17 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>3918786000010295026</t>
+          <t>3918786000010295054</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>KHADYA AMADE SILIMO</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>KHADYA AMADE SILIMO</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
@@ -4381,12 +4341,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>32100</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>13430</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4416,17 +4376,22 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8800</t>
+          <t>675</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>4625</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>3918786000010573014</t>
+          <t>3918786000010573018</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4444,6 +4409,11 @@
           <t>NAMPULA</t>
         </is>
       </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
           <t>Sim</t>
@@ -4454,6 +4424,11 @@
           <t>07-Jul-2026</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Passou a comprar num fornecedor mais proximo, reduzindo assim a emissao de pegada de carbono</t>
+        </is>
+      </c>
       <c r="V28" t="inlineStr">
         <is>
           <t>Luisa</t>
@@ -4461,7 +4436,12 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Segundo Mes de Implementação</t>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -4481,27 +4461,27 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>3918786000010295052</t>
+          <t>3918786000010295054</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>KHADYA AMADE SILIMO</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>KHADYA AMADE SILIMO</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Quarta Semana</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -4528,12 +4508,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17500</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5940</t>
+          <t>740</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4563,17 +4543,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>10310</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3918786000010573012</t>
+          <t>3918786000010573016</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4598,7 +4578,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Investiu 3000</t>
+          <t>Investiu 1640</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -4613,7 +4593,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Primeiro Mes de Implementação</t>
+          <t>Segundo Mes de Implementação</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -4633,22 +4613,22 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>3918786000010295052</t>
+          <t>3918786000010295026</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>Quarta Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -4680,12 +4660,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20000</t>
+          <t>32100</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>13430</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4715,17 +4695,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>8800</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>9870</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3918786000010559036</t>
+          <t>3918786000010573014</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4750,7 +4730,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -4760,47 +4740,47 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>Primeiro Mes de Implementação</t>
+          <t>Segundo Mes de Implementação</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>3918786000010295018</t>
+          <t>3918786000010295052</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>CATIZA ABAI NURO SITE</t>
+          <t>JESSICA MARIA JOSE NAMUE</t>
         </is>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>CATIZA ABAI NURO SITE</t>
+          <t>JESSICA MARIA JOSE NAMUE</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>Quarta Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
@@ -4822,17 +4802,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17500</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4842,7 +4822,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4862,17 +4842,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10310</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>3918786000010559034</t>
+          <t>3918786000010573012</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4892,12 +4872,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>Investiu 3000</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>03-Jul-2026</t>
+          <t>07-Jul-2026</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -4927,17 +4912,17 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>3918786000010295062</t>
+          <t>3918786000010295052</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>JESSICA MARIA JOSE NAMUE</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>JESSICA MARIA JOSE NAMUE</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
@@ -4974,12 +4959,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20000</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5009,17 +4994,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>450</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16550</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>3918786000010559032</t>
+          <t>3918786000010559036</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -5059,32 +5044,32 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>3918786000010295042</t>
+          <t>3918786000010295018</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
@@ -5094,7 +5079,7 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
@@ -5121,12 +5106,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5136,7 +5121,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -5161,12 +5146,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>3918786000010559030</t>
+          <t>3918786000010559034</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5206,32 +5191,32 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>3918786000010295038</t>
+          <t>3918786000010295062</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>FRANCISCA LUCIANO BOMES</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>FRANCISCA LUCIANO BOMES</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
@@ -5241,7 +5226,7 @@
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
@@ -5268,7 +5253,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5308,12 +5293,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>3918786000010559028</t>
+          <t>3918786000010559032</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5368,17 +5353,17 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>3918786000010295016</t>
+          <t>3918786000010295042</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
@@ -5415,52 +5400,52 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>2800</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3918786000010559026</t>
+          <t>3918786000010559030</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5500,32 +5485,32 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>3918786000010295012</t>
+          <t>3918786000010295038</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
@@ -5535,7 +5520,7 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
@@ -5562,52 +5547,52 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>1810</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>3918786000010559024</t>
+          <t>3918786000010559028</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5627,7 +5612,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -5647,32 +5632,32 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>3918786000010295088</t>
+          <t>3918786000010295016</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>SUZANA JOAQUIM VAQUINA</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>SUZANA JOAQUIM VAQUINA</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
@@ -5754,7 +5739,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>3918786000010559022</t>
+          <t>3918786000010559026</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5809,17 +5794,17 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>3918786000010295024</t>
+          <t>3918786000010295012</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>DULQUIFAL ASSANE SIMBA</t>
+          <t>ASSINA ABDALA ABDULSATAR</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
-          <t>DULQUIFAL ASSANE SIMBA</t>
+          <t>ASSINA ABDALA ABDULSATAR</t>
         </is>
       </c>
       <c r="AE37" t="inlineStr">
@@ -5856,7 +5841,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5871,7 +5856,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -5891,17 +5876,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>3918786000010559020</t>
+          <t>3918786000010559024</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5921,7 +5906,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -5941,32 +5926,32 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>3918786000010295090</t>
+          <t>3918786000010295088</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AE38" t="inlineStr">
@@ -6003,12 +5988,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13650</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6018,7 +6003,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -6038,17 +6023,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>7660</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>3918786000010516002</t>
+          <t>3918786000010559022</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -6068,12 +6053,12 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -6103,17 +6088,17 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>3918786000010295058</t>
+          <t>3918786000010295024</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t>DULQUIFAL ASSANE SIMBA</t>
         </is>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t>DULQUIFAL ASSANE SIMBA</t>
         </is>
       </c>
       <c r="AE39" t="inlineStr">
@@ -6150,14 +6135,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>true</t>
@@ -6165,7 +6150,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -6185,22 +6170,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Nao produziu na semana por motivos de doença</t>
+          <t>790</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>3918786000010502011</t>
+          <t>3918786000010559020</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -6220,12 +6200,12 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>29-Jun-2026</t>
+          <t>03-Jul-2026</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -6240,32 +6220,32 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>3918786000010295010</t>
+          <t>3918786000010295090</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>ARISTINA RABIA JULIO MANUEL</t>
+          <t>TEODORA MANUEL BRAS</t>
         </is>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>ARISTINA RABIA JULIO MANUEL</t>
+          <t>TEODORA MANUEL BRAS</t>
         </is>
       </c>
       <c r="AE40" t="inlineStr">
@@ -6302,12 +6282,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>13650</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>640</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6317,7 +6297,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -6337,17 +6317,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5350</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>3918786000010478026</t>
+          <t>3918786000010516002</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -6367,12 +6347,12 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>29-Jun-2026</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -6402,22 +6382,22 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>3918786000010295036</t>
+          <t>3918786000010295058</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
         </is>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
         </is>
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>Terceira Semana</t>
+          <t>Quarta Semana</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -6494,12 +6474,12 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>lucro zero (esta no período de criação de frangos)</t>
+          <t>Nao produziu na semana por motivos de doença</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>3918786000010478024</t>
+          <t>3918786000010502011</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6524,7 +6504,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>29-Jun-2026</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -6539,37 +6519,37 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>3918786000010295018</t>
+          <t>3918786000010295010</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>CATIZA ABAI NURO SITE</t>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>CATIZA ABAI NURO SITE</t>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
         </is>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>Terceira Semana</t>
+          <t>Quarta Semana</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -6601,12 +6581,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>700</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6636,17 +6616,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>700</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>3918786000010478022</t>
+          <t>3918786000010478026</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6666,7 +6646,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -6686,32 +6666,32 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>3918786000010295058</t>
+          <t>3918786000010295036</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AE43" t="inlineStr">
@@ -6748,7 +6728,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6788,12 +6768,17 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>lucro zero (esta no período de criação de frangos)</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>3918786000010478020</t>
+          <t>3918786000010478024</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6848,17 +6833,17 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>3918786000010295016</t>
+          <t>3918786000010295018</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AE44" t="inlineStr">
@@ -6895,12 +6880,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10056</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>610</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6910,59 +6895,59 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3450</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1090</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>3918786000010478022</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>4696</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>3918786000010478018</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
       <c r="T45" t="inlineStr">
         <is>
           <t>24-Jun-2026</t>
@@ -6980,32 +6965,32 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>3918786000010295054</t>
+          <t>3918786000010295058</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr">
@@ -7042,7 +7027,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -7057,7 +7042,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -7082,12 +7067,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>3918786000010478016</t>
+          <t>3918786000010478020</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -7107,7 +7092,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -7127,32 +7112,32 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>3918786000010295038</t>
+          <t>3918786000010295016</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>FRANCISCA LUCIANO BOMES</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>FRANCISCA LUCIANO BOMES</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr">
@@ -7189,12 +7174,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>10056</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2545</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7224,17 +7209,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>3918786000010478014</t>
+          <t>3918786000010478018</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -7254,7 +7239,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -7289,17 +7274,17 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>3918786000010295052</t>
+          <t>3918786000010295054</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>KHADYA AMADE SILIMO</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>KHADYA AMADE SILIMO</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr">
@@ -7336,12 +7321,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>900</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7371,17 +7356,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>3918786000010478012</t>
+          <t>3918786000010478016</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -7421,32 +7406,32 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>3918786000010295042</t>
+          <t>3918786000010295038</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr">
@@ -7478,84 +7463,79 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>8500</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2545</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>6885</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>5355</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>3918786000010478014</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>3170</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2645</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Investiu 500 em formas para testar um novo servico</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>3918786000010478010</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
       <c r="T49" t="inlineStr">
         <is>
           <t>24-Jun-2026</t>
@@ -7588,17 +7568,17 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>3918786000010295026</t>
+          <t>3918786000010295052</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>JESSICA MARIA JOSE NAMUE</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>JESSICA MARIA JOSE NAMUE</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr">
@@ -7635,52 +7615,52 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>1570</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>3918786000010478008</t>
+          <t>3918786000010478012</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7735,17 +7715,17 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>3918786000010295012</t>
+          <t>3918786000010295042</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr">
@@ -7777,17 +7757,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7797,7 +7777,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -7817,17 +7797,22 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2645</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Investiu 500 em formas para testar um novo servico</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>3918786000010478006</t>
+          <t>3918786000010478010</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7882,17 +7867,17 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>3918786000010295024</t>
+          <t>3918786000010295026</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>DULQUIFAL ASSANE SIMBA</t>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>DULQUIFAL ASSANE SIMBA</t>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr">
@@ -7929,52 +7914,52 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>3918786000010478004</t>
+          <t>3918786000010478008</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7994,7 +7979,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
@@ -8029,22 +8014,22 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>3918786000010295024</t>
+          <t>3918786000010295012</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>DULQUIFAL ASSANE SIMBA</t>
+          <t>ASSINA ABDALA ABDULSATAR</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>DULQUIFAL ASSANE SIMBA</t>
+          <t>ASSINA ABDALA ABDULSATAR</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -8121,7 +8106,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>3918786000010478002</t>
+          <t>3918786000010478006</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -8191,7 +8176,7 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -8266,14 +8251,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>nao produziu durante a semana porque estava doente</t>
-        </is>
-      </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>3918786000010471004</t>
+          <t>3918786000010478004</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -8313,37 +8293,37 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>3918786000010295010</t>
+          <t>3918786000010295024</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>ARISTINA RABIA JULIO MANUEL</t>
+          <t>DULQUIFAL ASSANE SIMBA</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>ARISTINA RABIA JULIO MANUEL</t>
+          <t>DULQUIFAL ASSANE SIMBA</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>Terceira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -8420,7 +8400,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>3918786000010471002</t>
+          <t>3918786000010478002</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -8460,37 +8440,37 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>3918786000010295044</t>
+          <t>3918786000010295024</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>GRACA CHICO PAULO VAGOS</t>
+          <t>DULQUIFAL ASSANE SIMBA</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>GRACA CHICO PAULO VAGOS</t>
+          <t>DULQUIFAL ASSANE SIMBA</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>Terceira Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -8522,7 +8502,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -8562,12 +8542,17 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>nao produziu durante a semana porque estava doente</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>3918786000010445192</t>
+          <t>3918786000010471004</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -8592,7 +8577,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -8607,32 +8592,32 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>3918786000010295056</t>
+          <t>3918786000010295010</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr">
@@ -8714,7 +8699,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>3918786000010445190</t>
+          <t>3918786000010471002</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -8739,7 +8724,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>22-Jun-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -8769,17 +8754,17 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>3918786000010295088</t>
+          <t>3918786000010295044</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>SUZANA JOAQUIM VAQUINA</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>SUZANA JOAQUIM VAQUINA</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr">
@@ -8816,12 +8801,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2975</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -8856,12 +8841,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>3918786000010445188</t>
+          <t>3918786000010445192</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -8881,7 +8866,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
@@ -8916,17 +8901,17 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>3918786000010295090</t>
+          <t>3918786000010295056</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr">
@@ -9006,14 +8991,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Nao produziu durante a semana por motivos de doença</t>
-        </is>
-      </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>3918786000010445186</t>
+          <t>3918786000010445190</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -9053,32 +9033,32 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>3918786000010295062</t>
+          <t>3918786000010295088</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr">
@@ -9115,12 +9095,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -9150,17 +9130,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>10080</t>
+          <t>305</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>3918786000010408006</t>
+          <t>3918786000010445188</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -9180,12 +9160,12 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>22-Jun-2026</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -9200,37 +9180,37 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>3918786000010295036</t>
+          <t>3918786000010295090</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t>TEODORA MANUEL BRAS</t>
         </is>
       </c>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t>TEODORA MANUEL BRAS</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -9305,9 +9285,14 @@
           <t>0</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Nao produziu durante a semana por motivos de doença</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>3918786000010408004</t>
+          <t>3918786000010445186</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -9332,7 +9317,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>18-Jun-2026</t>
+          <t>22-Jun-2026</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -9347,37 +9332,37 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>3918786000010295088</t>
+          <t>3918786000010295062</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>SUZANA JOAQUIM VAQUINA</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>SUZANA JOAQUIM VAQUINA</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Terceira Semana</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -9409,12 +9394,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>620</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -9444,17 +9429,17 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>3918786000010408002</t>
+          <t>3918786000010408006</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -9494,32 +9479,32 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>3918786000010295088</t>
+          <t>3918786000010295036</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>SUZANA JOAQUIM VAQUINA</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>SUZANA JOAQUIM VAQUINA</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr">
@@ -9556,12 +9541,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -9571,7 +9556,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -9591,17 +9576,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>3918786000010403026</t>
+          <t>3918786000010408004</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -9621,12 +9606,12 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -9641,32 +9626,32 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>3918786000010295052</t>
+          <t>3918786000010295088</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr">
@@ -9748,7 +9733,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>3918786000010403024</t>
+          <t>3918786000010408002</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -9768,12 +9753,12 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>17-Jun-2026</t>
+          <t>18-Jun-2026</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -9803,22 +9788,22 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>3918786000010295044</t>
+          <t>3918786000010295088</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>GRACA CHICO PAULO VAGOS</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>GRACA CHICO PAULO VAGOS</t>
+          <t>SUZANA JOAQUIM VAQUINA</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -9850,12 +9835,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -9885,17 +9870,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>3918786000010403022</t>
+          <t>3918786000010403026</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -9935,32 +9920,32 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>3918786000010295090</t>
+          <t>3918786000010295052</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>JESSICA MARIA JOSE NAMUE</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>JESSICA MARIA JOSE NAMUE</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr">
@@ -9997,12 +9982,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -10012,59 +9997,59 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>3918786000010403024</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>3665</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>3918786000010403020</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
       <c r="T66" t="inlineStr">
         <is>
           <t>17-Jun-2026</t>
@@ -10082,32 +10067,32 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>3918786000010295062</t>
+          <t>3918786000010295044</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr">
@@ -10144,12 +10129,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>450</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>375</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -10184,12 +10169,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>75</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>3918786000010403018</t>
+          <t>3918786000010403022</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -10229,32 +10214,32 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>3918786000010295054</t>
+          <t>3918786000010295090</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>TEODORA MANUEL BRAS</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>TEODORA MANUEL BRAS</t>
         </is>
       </c>
       <c r="AE67" t="inlineStr">
@@ -10286,84 +10271,79 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>4800</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>835</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>25175</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>1880</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>3918786000010403020</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>4470</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>18825</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>3918786000010403016</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>Investiu uma parte do lucro</t>
-        </is>
-      </c>
       <c r="T68" t="inlineStr">
         <is>
           <t>17-Jun-2026</t>
@@ -10396,17 +10376,17 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>3918786000010295036</t>
+          <t>3918786000010295062</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AE68" t="inlineStr">
@@ -10443,12 +10423,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -10483,12 +10463,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>3918786000010403014</t>
+          <t>3918786000010403018</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -10528,32 +10508,32 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>3918786000010295038</t>
+          <t>3918786000010295054</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>FRANCISCA LUCIANO BOMES</t>
+          <t>KHADYA AMADE SILIMO</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>FRANCISCA LUCIANO BOMES</t>
+          <t>KHADYA AMADE SILIMO</t>
         </is>
       </c>
       <c r="AE69" t="inlineStr">
@@ -10585,17 +10565,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>25175</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -10625,17 +10605,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>18825</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>3918786000010403012</t>
+          <t>3918786000010403016</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -10658,6 +10638,11 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Investiu uma parte do lucro</t>
+        </is>
+      </c>
       <c r="T70" t="inlineStr">
         <is>
           <t>17-Jun-2026</t>
@@ -10675,37 +10660,37 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>3918786000010295038</t>
+          <t>3918786000010295036</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>FRANCISCA LUCIANO BOMES</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>FRANCISCA LUCIANO BOMES</t>
+          <t>FILOMENA AMINA DOMINGOS ALVEZ</t>
         </is>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -10737,12 +10722,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -10772,17 +10757,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>850</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>3918786000010403010</t>
+          <t>3918786000010403014</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -10822,37 +10807,37 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>3918786000010295016</t>
+          <t>3918786000010295038</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -10884,12 +10869,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -10919,17 +10904,17 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>3918786000010403008</t>
+          <t>3918786000010403012</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -10949,7 +10934,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
@@ -10969,37 +10954,37 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>3918786000010295016</t>
+          <t>3918786000010295038</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
+          <t>FRANCISCA LUCIANO BOMES</t>
         </is>
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -11031,12 +11016,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>9050</t>
+          <t>3600</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11066,17 +11051,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>190</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>3918786000010403006</t>
+          <t>3918786000010403010</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -11116,37 +11101,37 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>3918786000010295058</t>
+          <t>3918786000010295016</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -11178,12 +11163,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>5310</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>2150</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -11213,17 +11198,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>3918786000010403004</t>
+          <t>3918786000010403008</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -11243,12 +11228,12 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -11278,17 +11263,17 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>3918786000010295026</t>
+          <t>3918786000010295016</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>BENUA FERNANDO VALENTIM INACIO BENE</t>
         </is>
       </c>
       <c r="AE74" t="inlineStr">
@@ -11325,12 +11310,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>660</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -11340,7 +11325,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -11360,17 +11345,17 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>870</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>7520</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>3918786000010403002</t>
+          <t>3918786000010403006</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -11390,12 +11375,12 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>17-Jun-2026</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -11410,32 +11395,32 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>3918786000010295028</t>
+          <t>3918786000010295058</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>ESMERALDA JORGE MURIRIUA</t>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>ESMERALDA JORGE MURIRIUA</t>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
         </is>
       </c>
       <c r="AE75" t="inlineStr">
@@ -11472,12 +11457,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>240</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -11507,17 +11492,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>520</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>3918786000010395008</t>
+          <t>3918786000010403004</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -11557,32 +11542,32 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>3918786000010295056</t>
+          <t>3918786000010295026</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
         </is>
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
         </is>
       </c>
       <c r="AE76" t="inlineStr">
@@ -11619,12 +11604,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>33900</t>
+          <t>7600</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -11634,7 +11619,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -11654,17 +11639,17 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>10500</t>
+          <t>1390</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>3918786000010395006</t>
+          <t>3918786000010403002</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -11684,7 +11669,7 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
@@ -11719,17 +11704,17 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>3918786000010295018</t>
+          <t>3918786000010295028</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>CATIZA ABAI NURO SITE</t>
+          <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>CATIZA ABAI NURO SITE</t>
+          <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
       <c r="AE77" t="inlineStr">
@@ -11766,7 +11751,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>36000</t>
+          <t>350</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -11801,17 +11786,17 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>35400</t>
+          <t>350</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>3918786000010395004</t>
+          <t>3918786000010395008</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -11836,7 +11821,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -11851,37 +11836,37 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>3918786000010295018</t>
+          <t>3918786000010295056</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>CATIZA ABAI NURO SITE</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>CATIZA ABAI NURO SITE</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -11913,12 +11898,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1510</t>
+          <t>33900</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>500</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -11948,22 +11933,17 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>22900</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>-235</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">teve prejuízo na semana porque estava ocupada e nao conseguiu produzir </t>
+          <t>10500</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>3918786000010395002</t>
+          <t>3918786000010395006</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -12018,17 +11998,17 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>3918786000010295042</t>
+          <t>3918786000010295018</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AE79" t="inlineStr">
@@ -12065,77 +12045,77 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
+          <t>36000</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
           <t>600</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>35400</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>3918786000010395004</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>3918786000010390008</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>15-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -12165,22 +12145,22 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>3918786000010295012</t>
+          <t>3918786000010295018</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>CATIZA ABAI NURO SITE</t>
         </is>
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>Segunda Semana</t>
+          <t>Primeira Semana</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -12212,12 +12192,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -12247,17 +12227,22 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>-235</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">teve prejuízo na semana porque estava ocupada e nao conseguiu produzir </t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>3918786000010390006</t>
+          <t>3918786000010395002</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -12297,32 +12282,32 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>3918786000010295010</t>
+          <t>3918786000010295042</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>ARISTINA RABIA JULIO MANUEL</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>ARISTINA RABIA JULIO MANUEL</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AE81" t="inlineStr">
@@ -12354,79 +12339,79 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2180</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>1320</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>3918786000010390008</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>760</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>3918786000010390004</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
       <c r="T82" t="inlineStr">
         <is>
           <t>15-Jun-2026</t>
@@ -12459,17 +12444,17 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>3918786000010295040</t>
+          <t>3918786000010295012</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>ASSINA ABDALA ABDULSATAR</t>
         </is>
       </c>
       <c r="AD82" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>ASSINA ABDALA ABDULSATAR</t>
         </is>
       </c>
       <c r="AE82" t="inlineStr">
@@ -12506,12 +12491,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -12521,7 +12506,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -12541,17 +12526,17 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>470</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>3918786000010390002</t>
+          <t>3918786000010390006</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -12571,7 +12556,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -12621,7 +12606,7 @@
       </c>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -12648,17 +12633,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -12668,7 +12653,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -12688,17 +12673,17 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>760</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>3918786000010380004</t>
+          <t>3918786000010390004</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -12723,7 +12708,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -12738,37 +12723,37 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>3918786000010295044</t>
+          <t>3918786000010295040</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>GRACA CHICO PAULO VAGOS</t>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
         </is>
       </c>
       <c r="AD84" t="inlineStr">
         <is>
-          <t>GRACA CHICO PAULO VAGOS</t>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
         </is>
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>Primeira Semana</t>
+          <t>Segunda Semana</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -12800,12 +12785,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -12815,7 +12800,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -12835,17 +12820,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>3918786000010380002</t>
+          <t>3918786000010390002</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -12865,12 +12850,12 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>15-Jun-2026</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -12885,32 +12870,32 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>3918786000010295062</t>
+          <t>3918786000010295010</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
         </is>
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>MARAVILHA JANUARIO  CARIA</t>
+          <t>ARISTINA RABIA JULIO MANUEL</t>
         </is>
       </c>
       <c r="AE85" t="inlineStr">
@@ -12947,12 +12932,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>550</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -12962,62 +12947,62 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>3918786000010380004</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>1680</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>3918786000010379008</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -13032,32 +13017,32 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>3918786000010295042</t>
+          <t>3918786000010295044</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AD86" t="inlineStr">
         <is>
-          <t>GLORIA DA CONSTANCIA LOJA</t>
+          <t>GRACA CHICO PAULO VAGOS</t>
         </is>
       </c>
       <c r="AE86" t="inlineStr">
@@ -13094,12 +13079,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>10900</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -13129,17 +13114,17 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>3918786000010379006</t>
+          <t>3918786000010380002</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -13179,32 +13164,32 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>3918786000010295056</t>
+          <t>3918786000010295062</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>LATIZA AIUBA</t>
+          <t>MARAVILHA JANUARIO  CARIA</t>
         </is>
       </c>
       <c r="AE87" t="inlineStr">
@@ -13241,12 +13226,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>10130</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -13276,17 +13261,17 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>270</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>3918786000010379004</t>
+          <t>3918786000010379008</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -13311,7 +13296,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -13341,17 +13326,17 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>3918786000010295040</t>
+          <t>3918786000010295042</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr">
         <is>
-          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
+          <t>GLORIA DA CONSTANCIA LOJA</t>
         </is>
       </c>
       <c r="AE88" t="inlineStr">
@@ -13388,12 +13373,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -13423,17 +13408,17 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>3918786000010379002</t>
+          <t>3918786000010379006</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -13473,32 +13458,32 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>3918786000010287026</t>
+          <t>3918786000010287028</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>3918786000010295058</t>
+          <t>3918786000010295056</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AD89" t="inlineStr">
         <is>
-          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
+          <t>LATIZA AIUBA</t>
         </is>
       </c>
       <c r="AE89" t="inlineStr">
@@ -13535,12 +13520,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>17495</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>8960</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -13570,17 +13555,17 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>600</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>3918786000010367048</t>
+          <t>3918786000010379004</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -13635,17 +13620,17 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>3918786000010295026</t>
+          <t>3918786000010295040</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr">
         <is>
-          <t>ELVIRA LOGRIGUES  MATANHA</t>
+          <t>GLORIA  GERMANO DO ROSARIO RIBEIRO</t>
         </is>
       </c>
       <c r="AE90" t="inlineStr">
@@ -13677,84 +13662,79 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>9125</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>1595</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>8410</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>3918786000010379002</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>7430</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>3918786000010367046</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>Investiu 160 na compra de formas novas</t>
-        </is>
-      </c>
       <c r="T91" t="inlineStr">
         <is>
           <t>08-Jun-2026</t>
@@ -13772,32 +13752,32 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>3918786000010287030</t>
+          <t>3918786000010287026</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+          <t>Prestação de serviços (ornamentação de eventos, microcrédito, salão de cabeleleiro, takeaway etc)</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>3918786000010295054</t>
+          <t>3918786000010295058</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
         </is>
       </c>
       <c r="AD91" t="inlineStr">
         <is>
-          <t>KHADYA AMADE SILIMO</t>
+          <t>LUCIA  EUGENIO LUCIANO VIEGAS</t>
         </is>
       </c>
       <c r="AE91" t="inlineStr">
@@ -13829,87 +13809,82 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>17495</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>8960</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>4670</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>3865</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>3918786000010367048</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>3918786000004909039</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>3918786000010358004</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>3918786000004909063</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>Sim</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>Trabalhar na visibilidade do negócio (fazer um plano de postagem)</t>
-        </is>
-      </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>09-Jun-2026</t>
+          <t>08-Jun-2026</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
@@ -13939,17 +13914,17 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>3918786000010295012</t>
+          <t>3918786000010295026</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
         </is>
       </c>
       <c r="AD92" t="inlineStr">
         <is>
-          <t>ASSINA ABDALA ABDULSATAR</t>
+          <t>ELVIRA LOGRIGUES  MATANHA</t>
         </is>
       </c>
       <c r="AE92" t="inlineStr">
@@ -13981,17 +13956,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>18500</t>
+          <t>9125</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -14021,17 +13996,17 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>11150</t>
+          <t>7430</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>3918786000010358002</t>
+          <t>3918786000010367046</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -14054,6 +14029,11 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Investiu 160 na compra de formas novas</t>
+        </is>
+      </c>
       <c r="T93" t="inlineStr">
         <is>
           <t>08-Jun-2026</t>
@@ -14086,17 +14066,17 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>3918786000010295052</t>
+          <t>3918786000010295054</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>KHADYA AMADE SILIMO</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>JESSICA MARIA JOSE NAMUE</t>
+          <t>KHADYA AMADE SILIMO</t>
         </is>
       </c>
       <c r="AE93" t="inlineStr">
@@ -14128,17 +14108,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -14168,17 +14148,17 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>3918786000010356002</t>
+          <t>3918786000010358004</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -14201,9 +14181,14 @@
           <t>Sim</t>
         </is>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Trabalhar na visibilidade do negócio (fazer um plano de postagem)</t>
+        </is>
+      </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>08-Jun-2026</t>
+          <t>09-Jun-2026</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
@@ -14218,32 +14203,32 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>3918786000010287028</t>
+          <t>3918786000010287030</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>3918786000010295090</t>
+          <t>3918786000010295012</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>ASSINA ABDALA ABDULSATAR</t>
         </is>
       </c>
       <c r="AD94" t="inlineStr">
         <is>
-          <t>TEODORA MANUEL BRAS</t>
+          <t>ASSINA ABDALA ABDULSATAR</t>
         </is>
       </c>
       <c r="AE94" t="inlineStr">
@@ -14280,140 +14265,434 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
+          <t>18500</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>5850</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>11150</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>3918786000010358002</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>3918786000010287030</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>3918786000010295052</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>JESSICA MARIA JOSE NAMUE</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>JESSICA MARIA JOSE NAMUE</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>3918786000004909039</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>3918786000010356002</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>3918786000004909063</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>08-Jun-2026</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Primeiro Mes de Implementação</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>3918786000010287028</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>Produção e venda de produtos não alimentares (Artesanato, etc: Com transformação de prod.)</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>3918786000010295090</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>TEODORA MANUEL BRAS</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>TEODORA MANUEL BRAS</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>Primeira Semana</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>3918786000007161003</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
           <t>13160</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>3705</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
         <is>
           <t>3918786000004909039</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>PAM VERDE</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>PAM VERDE</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
         <is>
           <t>1005</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>8450</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t>3918786000010353002</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr">
+      <c r="N97" t="inlineStr">
         <is>
           <t>3918786000004909063</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>NAMPULA</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr">
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>NAMPULA</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
-      <c r="T95" t="inlineStr">
+      <c r="T97" t="inlineStr">
         <is>
           <t>08-Jun-2026</t>
         </is>
       </c>
-      <c r="V95" t="inlineStr">
+      <c r="V97" t="inlineStr">
         <is>
           <t>Luisa</t>
         </is>
       </c>
-      <c r="W95" t="inlineStr">
+      <c r="W97" t="inlineStr">
         <is>
           <t>Primeiro Mes de Implementação</t>
         </is>
       </c>
-      <c r="Y95" t="inlineStr">
+      <c r="Y97" t="inlineStr">
         <is>
           <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
+      <c r="Z97" t="inlineStr">
         <is>
           <t>3918786000010287030</t>
         </is>
       </c>
-      <c r="AA95" t="inlineStr">
+      <c r="AA97" t="inlineStr">
         <is>
           <t>Produção e venda de produtos alimentares (bolos, salgados, comidas, etc :transformação de prod)</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
+      <c r="AB97" t="inlineStr">
         <is>
           <t>3918786000010295028</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
+      <c r="AC97" t="inlineStr">
         <is>
           <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
-      <c r="AD95" t="inlineStr">
+      <c r="AD97" t="inlineStr">
         <is>
           <t>ESMERALDA JORGE MURIRIUA</t>
         </is>
       </c>
-      <c r="AE95" t="inlineStr">
+      <c r="AE97" t="inlineStr">
         <is>
           <t>Primeira Semana</t>
         </is>
       </c>
-      <c r="AF95" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AG95" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="AH95" t="inlineStr">
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
         <is>
           <t>3918786000007161003</t>
         </is>
       </c>
-      <c r="AI95" t="inlineStr">
+      <c r="AI97" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -14680,13 +14959,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C67166C3-1E73-4FCB-A6EB-39B4C8EF44F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1775501E-3795-4BCE-A45D-63B5223D0107}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73D7E7B6-9E0C-4626-8BF7-B9D8EAB7262A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{691B1903-58A6-46EC-BCC1-443205991256}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C07FEA97-047A-46E5-90DC-161399A98BD3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3EABE4D-8B1B-47AD-9D88-CF6B2B5A8A07}"/>
 </file>
--- a/Financeiro_Report.xlsx
+++ b/Financeiro_Report.xlsx
@@ -31733,13 +31733,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6398845F-9212-4610-BE7D-65CDE4D29B07}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BF5AE61-9896-43D2-9BD5-772FC45D03EC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48C4C49C-6AEB-4A4A-8BF5-1739F7E1F8F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBB82439-B654-4221-B0FF-BE574EC74CF0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AA6967F-CCFB-44C1-9BD6-E3CC19A81CE1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A2C4497-03F6-41DA-AEE1-E888C052840E}"/>
 </file>